--- a/src/data/downloads/1919_Constituent_Assembly_Elections_main_19190214_data_202604222211119.xlsx
+++ b/src/data/downloads/1919_Constituent_Assembly_Elections_main_19190214_data_202604222211119.xlsx
@@ -6,14 +6,14 @@
   <sheets>
     <sheet sheetId="1" name="PR - Districts" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Candidates - კანდიდატები" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="About - მეტამონაცემები" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="About - Metadata" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="180">
   <si>
     <t xml:space="preserve">District ID
 ოლქის კოდი</t>
@@ -560,13 +560,13 @@
     <t>Archive</t>
   </si>
   <si>
-    <t>Comprehensive Election Data Archive of Georgia (CEDAG)</t>
+    <t>Georgia Election Data Archive (GEDA)</t>
   </si>
   <si>
     <t>Website</t>
   </si>
   <si>
-    <t>https://electionsdata.ge</t>
+    <t>https://electionsdata.ge/elections?type=parliamentary&amp;election=parl_1919</t>
   </si>
   <si>
     <t>Author</t>
@@ -575,77 +575,65 @@
     <t>David Sichinava</t>
   </si>
   <si>
+    <t>Election (EN)</t>
+  </si>
+  <si>
+    <t>1919 Constituent Assembly Elections</t>
+  </si>
+  <si>
+    <t>Election (KA)</t>
+  </si>
+  <si>
+    <t>1919 წლის დამფუძნებელი კრების არჩევნები</t>
+  </si>
+  <si>
+    <t>Election ID</t>
+  </si>
+  <si>
+    <t>parl_1919</t>
+  </si>
+  <si>
+    <t>Election Type</t>
+  </si>
+  <si>
+    <t>parliamentary</t>
+  </si>
+  <si>
+    <t>Election Date</t>
+  </si>
+  <si>
+    <t>1919-02-14 - 1919-02-16</t>
+  </si>
+  <si>
+    <t>File Generated</t>
+  </si>
+  <si>
+    <t>2026-04-30T18:50:28.616Z</t>
+  </si>
+  <si>
+    <t>Data Source</t>
+  </si>
+  <si>
+    <t>National Archives of Georgia. Central Historical Archive, Fund N1834, Descr. 2, Fol. 59, Pg. 63; National Archives of Georgia. Central Historical Archive, Fund N1834, Descr. 2, Fol. 17, Pg. 25</t>
+  </si>
+  <si>
     <t>Citation (APA)</t>
   </si>
   <si>
-    <t>Sichinava, D. (2026). Results of the 1919 Constituent Assembly Elections. Comprehensive Election Data Archive of Georgia (CEDAG). https://electionsdata.ge/parl_1919</t>
-  </si>
-  <si>
-    <t>Citation (Chicago)</t>
-  </si>
-  <si>
-    <t>Sichinava, David. 2026. "Results of the 1919 Constituent Assembly Elections." Comprehensive Election Data Archive of Georgia (CEDAG). https://electionsdata.ge/parl_1919.</t>
-  </si>
-  <si>
-    <t>Election (EN)</t>
-  </si>
-  <si>
-    <t>1919 Constituent Assembly Elections</t>
-  </si>
-  <si>
-    <t>Election (KA)</t>
-  </si>
-  <si>
-    <t>1919 წლის დამფუძნებელი კრების არჩევნები</t>
-  </si>
-  <si>
-    <t>Election ID</t>
-  </si>
-  <si>
-    <t>parl_1919</t>
-  </si>
-  <si>
-    <t>Election Type</t>
-  </si>
-  <si>
-    <t>parliamentary</t>
-  </si>
-  <si>
-    <t>Election Date</t>
-  </si>
-  <si>
-    <t>1919-02-14 - 1919-02-16</t>
-  </si>
-  <si>
-    <t>Sub-election</t>
-  </si>
-  <si>
-    <t>Main Election</t>
-  </si>
-  <si>
-    <t>File Generated</t>
-  </si>
-  <si>
-    <t>2026-04-22T22:11:11.978Z</t>
-  </si>
-  <si>
-    <t>Data Source</t>
-  </si>
-  <si>
-    <t>Central Election Commission of Georgia (cesko.ge)</t>
+    <t>Sichinava, D. (2026). Results of the 1919 Constituent Assembly Elections. Georgia Election Data Archive (GEDA). https://electionsdata.ge/elections?type=parliamentary&amp;election=parl_1919</t>
   </si>
   <si>
     <t>License</t>
   </si>
   <si>
-    <t>Open data. Please cite CEDAG when using.</t>
+    <t>CC-BY-4.0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -668,10 +656,6 @@
       <sz val="9"/>
     </font>
     <font>
-      <sz val="9"/>
-    </font>
-    <font>
-      <i/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -709,7 +693,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -717,9 +701,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5818,7 +5799,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -5903,17 +5884,17 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="72" customWidth="1"/>
+    <col min="2" max="2" width="88" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -5944,7 +5925,7 @@
       <c r="A4" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5957,99 +5938,59 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>47</v>
+      <c r="A6" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>47</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B14" s="4" t="s">
         <v>179</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/src/data/downloads/1919_Constituent_Assembly_Elections_main_19190214_data_202604222211119.xlsx
+++ b/src/data/downloads/1919_Constituent_Assembly_Elections_main_19190214_data_202604222211119.xlsx
@@ -608,7 +608,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-04-30T18:50:28.616Z</t>
+    <t>2026-05-12T18:52:42.649Z</t>
   </si>
   <si>
     <t>Data Source</t>
